--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1116,107 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129805674</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91589</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sluten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465483</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6988087</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,1947 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129999049</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465595</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6988414</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 66 plantor och 1 vinterståndare inom ca 0,5 m2 yta intill en tall och gran på en upphöjd mossklädd yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129999056</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465481</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6988529</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129999047</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98698</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>465333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6988408</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129999037</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>465617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6988364</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129999054</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>465346</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6988362</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129999032</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>465393</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6988403</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en stående död gran (24 cm BHD) med andra hackspår av hackspett. Granen står ca 4 meter väster om ett dike. Runt fyndplatsen finns stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett. I skogsbeståndet finns även frekvent förekomst av barkskalade granar med både färska och äldre potentiella födosökspår efter tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129999040</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>465568</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6988182</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en klen sälg i granskog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129999014</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>465464</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6988331</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt i en upplyft granlåga i granskog.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129999034</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>465636</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6988535</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, enstaka ytliga på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129999033</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>465491</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6988514</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka men tydliga på en gran i granskog med bitvis högt och mycket högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved främsta av gran.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129999038</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56927</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>465735</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6988529</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129999055</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>465462</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6988495</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129999058</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>465509</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6988218</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129999048</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>465486</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6988507</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 1 vinterståndare inom ca 2 m2 yta intill  gran med sockel vid en glänta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129999039</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sluten/Gåxmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>465427</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6988282</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog. I denna skog finns även murkna/murknande björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129999049</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129999056</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>129999047</v>
       </c>
       <c r="B9" t="n">
-        <v>98698</v>
+        <v>98701</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129999037</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>129999054</v>
       </c>
       <c r="B11" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129999032</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,39 +1994,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129999040</v>
+        <v>129999014</v>
       </c>
       <c r="B13" t="n">
-        <v>80218</v>
+        <v>91605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465568</v>
+        <v>465464</v>
       </c>
       <c r="R13" t="n">
-        <v>6988182</v>
+        <v>6988331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en klen sälg i granskog.</t>
+          <t>Rikligt i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,22 +2096,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2129,39 +2129,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129999014</v>
+        <v>129999040</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>80221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465464</v>
+        <v>465568</v>
       </c>
       <c r="R14" t="n">
-        <v>6988331</v>
+        <v>6988182</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt i en upplyft granlåga i granskog.</t>
+          <t>På en klen sälg i granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         <v>129999034</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>129999033</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>129999038</v>
       </c>
       <c r="B17" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129999055</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>129999058</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2913,61 +2913,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129999048</v>
+        <v>129999039</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465486</v>
+        <v>465427</v>
       </c>
       <c r="R20" t="n">
-        <v>6988507</v>
+        <v>6988282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 1 vinterståndare inom ca 2 m2 yta intill  gran med sockel vid en glänta i äldre granskog.</t>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog. I denna skog finns även murkna/murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3013,7 +3013,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3037,61 +3036,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129999039</v>
+        <v>129999048</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465427</v>
+        <v>465486</v>
       </c>
       <c r="R21" t="n">
-        <v>6988282</v>
+        <v>6988507</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3128,7 +3127,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i flerskiktad granskog. I denna skog finns även murkna/murknande björkhögstubbar för talltitans bohål.</t>
+          <t>Minst 30 plantor och 1 vinterståndare inom ca 2 m2 yta intill  gran med sockel vid en glänta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1343,37 +1343,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999056</v>
+        <v>129999047</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>98701</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465481</v>
+        <v>465333</v>
       </c>
       <c r="R8" t="n">
-        <v>6988529</v>
+        <v>6988408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1432,11 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1432,26 +1450,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,50 +1467,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999047</v>
+        <v>129999056</v>
       </c>
       <c r="B9" t="n">
-        <v>98701</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465333</v>
+        <v>465481</v>
       </c>
       <c r="R9" t="n">
-        <v>6988408</v>
+        <v>6988529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,11 +1543,6 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1576,6 +1556,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999037</v>
+        <v>129999054</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,29 +1604,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1636,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465617</v>
+        <v>465346</v>
       </c>
       <c r="R10" t="n">
-        <v>6988364</v>
+        <v>6988362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
+          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,6 +1680,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1728,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999054</v>
+        <v>129999037</v>
       </c>
       <c r="B11" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,24 +1735,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1766,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465346</v>
+        <v>465617</v>
       </c>
       <c r="R11" t="n">
-        <v>6988362</v>
+        <v>6988364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1807,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
+          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1816,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129999049</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,50 +1343,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999047</v>
+        <v>129999056</v>
       </c>
       <c r="B8" t="n">
-        <v>98701</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465333</v>
+        <v>465481</v>
       </c>
       <c r="R8" t="n">
-        <v>6988408</v>
+        <v>6988529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,11 +1419,6 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1450,6 +1432,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1467,37 +1469,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999056</v>
+        <v>129999047</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>98702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465481</v>
+        <v>465333</v>
       </c>
       <c r="R9" t="n">
-        <v>6988529</v>
+        <v>6988408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,6 +1558,11 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1556,26 +1576,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         <v>129999054</v>
       </c>
       <c r="B10" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>129999014</v>
       </c>
       <c r="B13" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>129999040</v>
       </c>
       <c r="B14" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129999055</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>129999058</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>129999048</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1343,37 +1343,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999056</v>
+        <v>129999047</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>98702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465481</v>
+        <v>465333</v>
       </c>
       <c r="R8" t="n">
-        <v>6988529</v>
+        <v>6988408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1432,11 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1432,26 +1450,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,50 +1467,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999047</v>
+        <v>129999056</v>
       </c>
       <c r="B9" t="n">
-        <v>98702</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1520,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465333</v>
+        <v>465481</v>
       </c>
       <c r="R9" t="n">
-        <v>6988408</v>
+        <v>6988529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,11 +1543,6 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1576,6 +1556,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129999049</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,50 +1343,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999047</v>
+        <v>129999056</v>
       </c>
       <c r="B8" t="n">
-        <v>98702</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465333</v>
+        <v>465481</v>
       </c>
       <c r="R8" t="n">
-        <v>6988408</v>
+        <v>6988529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,11 +1419,6 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1450,6 +1432,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1467,37 +1469,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999056</v>
+        <v>129999047</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>98719</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465481</v>
+        <v>465333</v>
       </c>
       <c r="R9" t="n">
-        <v>6988529</v>
+        <v>6988408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,6 +1558,11 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1556,26 +1576,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
         <v>129999054</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>129999014</v>
       </c>
       <c r="B13" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>129999040</v>
       </c>
       <c r="B14" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129999055</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>129999058</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>129999039</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>129999048</v>
       </c>
       <c r="B21" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999054</v>
+        <v>129999037</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,24 +1604,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1631,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465346</v>
+        <v>465617</v>
       </c>
       <c r="R10" t="n">
-        <v>6988362</v>
+        <v>6988364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
+          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,7 +1685,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1724,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999037</v>
+        <v>129999054</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,29 +1739,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1767,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465617</v>
+        <v>465346</v>
       </c>
       <c r="R11" t="n">
-        <v>6988364</v>
+        <v>6988362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1806,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
+          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,6 +1815,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999037</v>
+        <v>129999054</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>91659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,29 +1604,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1636,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465617</v>
+        <v>465346</v>
       </c>
       <c r="R10" t="n">
-        <v>6988364</v>
+        <v>6988362</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
+          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,6 +1680,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1728,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999054</v>
+        <v>129999037</v>
       </c>
       <c r="B11" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,24 +1735,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1766,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465346</v>
+        <v>465617</v>
       </c>
       <c r="R11" t="n">
-        <v>6988362</v>
+        <v>6988364</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1807,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
+          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,7 +1816,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>129805674</v>
       </c>
       <c r="B6" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>129999049</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129999047</v>
       </c>
       <c r="B8" t="n">
-        <v>98735</v>
+        <v>98737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>129999054</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>129999014</v>
       </c>
       <c r="B13" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>129999048</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 46938-2025 artfynd.xlsx
+++ b/artfynd/A 46938-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>129999049</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,50 +1343,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999047</v>
+        <v>129999056</v>
       </c>
       <c r="B8" t="n">
-        <v>98737</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465333</v>
+        <v>465481</v>
       </c>
       <c r="R8" t="n">
-        <v>6988408</v>
+        <v>6988529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,11 +1419,6 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1450,6 +1432,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1467,37 +1469,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999056</v>
+        <v>129999047</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>98824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465481</v>
+        <v>465333</v>
       </c>
       <c r="R9" t="n">
-        <v>6988529</v>
+        <v>6988408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,6 +1558,11 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 vinterståndare intill en gammal gran med sockel i granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1556,26 +1576,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999054</v>
+        <v>129999037</v>
       </c>
       <c r="B10" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,24 +1604,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1631,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465346</v>
+        <v>465617</v>
       </c>
       <c r="R10" t="n">
-        <v>6988362</v>
+        <v>6988364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
+          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,7 +1685,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1724,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999037</v>
+        <v>129999054</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,29 +1739,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1767,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465617</v>
+        <v>465346</v>
       </c>
       <c r="R11" t="n">
-        <v>6988364</v>
+        <v>6988362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1806,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka ca 5-6 meter upp på en gran vid hyggeskanten.</t>
+          <t>Flera fruktkroppar i en stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,6 +1815,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>129999032</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1994,39 +1994,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129999014</v>
+        <v>129999040</v>
       </c>
       <c r="B13" t="n">
-        <v>91641</v>
+        <v>80314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465464</v>
+        <v>465568</v>
       </c>
       <c r="R13" t="n">
-        <v>6988331</v>
+        <v>6988182</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt i en upplyft granlåga i granskog.</t>
+          <t>På en klen sälg i granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,22 +2096,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2129,39 +2129,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129999040</v>
+        <v>129999014</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465568</v>
+        <v>465464</v>
       </c>
       <c r="R14" t="n">
-        <v>6988182</v>
+        <v>6988331</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en klen sälg i granskog.</t>
+          <t>Rikligt i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         <v>129999034</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>129999033</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>129999038</v>
       </c>
       <c r="B17" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129999055</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>129999058</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2913,61 +2913,61 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129999039</v>
+        <v>129999048</v>
       </c>
       <c r="B20" t="n">
-        <v>57900</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465427</v>
+        <v>465486</v>
       </c>
       <c r="R20" t="n">
-        <v>6988282</v>
+        <v>6988507</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 1 individ med lockläte i flerskiktad granskog. I denna skog finns även murkna/murknande björkhögstubbar för talltitans bohål.</t>
+          <t>Minst 30 plantor och 1 vinterståndare inom ca 2 m2 yta intill  gran med sockel vid en glänta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3013,6 +3013,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3036,61 +3037,61 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129999048</v>
+        <v>129999039</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>57985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465486</v>
+        <v>465427</v>
       </c>
       <c r="R21" t="n">
-        <v>6988507</v>
+        <v>6988282</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3127,7 +3128,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 1 vinterståndare inom ca 2 m2 yta intill  gran med sockel vid en glänta i äldre granskog.</t>
+          <t>Minst 1 individ med lockläte i flerskiktad granskog. I denna skog finns även murkna/murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3136,7 +3137,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
